--- a/SWAEGB.xlsx
+++ b/SWAEGB.xlsx
@@ -100,7 +100,7 @@
     <t>20136451</t>
   </si>
   <si>
-    <t>NSCAFE AMERICANO 10S</t>
+    <t>NESCAFE AMRCN 10X2 G</t>
   </si>
   <si>
     <t>9</t>
